--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -248,8 +248,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -265,7 +273,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -273,12 +281,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -578,39 +604,39 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>44927</v>
       </c>
       <c r="B2">
@@ -642,7 +668,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>44958</v>
       </c>
       <c r="B3">
@@ -674,7 +700,7 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>44986</v>
       </c>
       <c r="B4">
@@ -706,7 +732,7 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>45017</v>
       </c>
       <c r="B5">
@@ -738,7 +764,7 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>45047</v>
       </c>
       <c r="B6">
@@ -770,7 +796,7 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>45078</v>
       </c>
       <c r="B7">
@@ -802,7 +828,7 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>45108</v>
       </c>
       <c r="B8">
@@ -834,7 +860,7 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>45139</v>
       </c>
       <c r="B9">
@@ -866,7 +892,7 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>45170</v>
       </c>
       <c r="B10">
@@ -898,7 +924,7 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>45200</v>
       </c>
       <c r="B11">
@@ -930,7 +956,7 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>45231</v>
       </c>
       <c r="B12">
@@ -962,7 +988,7 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>45261</v>
       </c>
       <c r="B13">
@@ -994,7 +1020,7 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>45292</v>
       </c>
       <c r="B14">
@@ -1026,7 +1052,7 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>45323</v>
       </c>
       <c r="B15">
@@ -1058,7 +1084,7 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>45352</v>
       </c>
       <c r="B16">
@@ -1090,7 +1116,7 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>45383</v>
       </c>
       <c r="B17">
@@ -1122,7 +1148,7 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>45413</v>
       </c>
       <c r="B18">
@@ -1154,7 +1180,7 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>45444</v>
       </c>
       <c r="B19">
@@ -1186,7 +1212,7 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>45474</v>
       </c>
       <c r="B20">
@@ -1218,7 +1244,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>45505</v>
       </c>
       <c r="B21">
@@ -1250,7 +1276,7 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>45536</v>
       </c>
       <c r="B22">
@@ -1282,7 +1308,7 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>45566</v>
       </c>
       <c r="B23">
@@ -1314,7 +1340,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>45597</v>
       </c>
       <c r="B24">
@@ -1346,7 +1372,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>45627</v>
       </c>
       <c r="B25">
@@ -1378,7 +1404,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>45658</v>
       </c>
       <c r="B26">
@@ -1410,7 +1436,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>45689</v>
       </c>
       <c r="B27">
@@ -1442,7 +1468,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>45717</v>
       </c>
       <c r="B28">
@@ -1474,7 +1500,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>45748</v>
       </c>
       <c r="B29">
@@ -1506,7 +1532,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>45778</v>
       </c>
       <c r="B30">
@@ -1538,7 +1564,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>45809</v>
       </c>
       <c r="B31">
@@ -1570,7 +1596,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>45839</v>
       </c>
       <c r="B32">
@@ -1602,7 +1628,7 @@
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>45870</v>
       </c>
       <c r="B33">
@@ -1634,7 +1660,7 @@
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>45901</v>
       </c>
       <c r="B34">
@@ -1666,7 +1692,7 @@
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>45931</v>
       </c>
       <c r="B35">
@@ -1698,7 +1724,7 @@
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>45962</v>
       </c>
       <c r="B36">
@@ -1730,7 +1756,7 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>45992</v>
       </c>
       <c r="B37">
@@ -1762,7 +1788,7 @@
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>46023</v>
       </c>
       <c r="B38">
@@ -1794,7 +1820,7 @@
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>46054</v>
       </c>
       <c r="B39">
@@ -1826,7 +1852,7 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>46082</v>
       </c>
       <c r="B40">
@@ -1858,7 +1884,7 @@
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>46113</v>
       </c>
       <c r="B41">
@@ -1890,7 +1916,7 @@
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>46143</v>
       </c>
       <c r="B42">
@@ -1922,7 +1948,7 @@
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <v>46174</v>
       </c>
       <c r="B43">
@@ -1954,7 +1980,7 @@
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>46204</v>
       </c>
       <c r="B44">
@@ -1986,7 +2012,7 @@
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>46235</v>
       </c>
       <c r="B45">
@@ -2018,7 +2044,7 @@
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>46266</v>
       </c>
       <c r="B46">
@@ -2050,7 +2076,7 @@
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <v>44927</v>
       </c>
       <c r="B47">
@@ -2082,7 +2108,7 @@
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>44958</v>
       </c>
       <c r="B48">
@@ -2114,7 +2140,7 @@
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>44986</v>
       </c>
       <c r="B49">
@@ -2146,7 +2172,7 @@
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>45017</v>
       </c>
       <c r="B50">
@@ -2178,7 +2204,7 @@
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="1">
+      <c r="A51" s="2">
         <v>45047</v>
       </c>
       <c r="B51">
@@ -2210,7 +2236,7 @@
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>45078</v>
       </c>
       <c r="B52">
@@ -2242,7 +2268,7 @@
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>45108</v>
       </c>
       <c r="B53">
@@ -2274,7 +2300,7 @@
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>45139</v>
       </c>
       <c r="B54">
@@ -2306,7 +2332,7 @@
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>45170</v>
       </c>
       <c r="B55">
@@ -2338,7 +2364,7 @@
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>45200</v>
       </c>
       <c r="B56">
@@ -2370,7 +2396,7 @@
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>45231</v>
       </c>
       <c r="B57">
@@ -2402,7 +2428,7 @@
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>45261</v>
       </c>
       <c r="B58">
@@ -2434,7 +2460,7 @@
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>45292</v>
       </c>
       <c r="B59">
@@ -2466,7 +2492,7 @@
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>45323</v>
       </c>
       <c r="B60">
@@ -2498,7 +2524,7 @@
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>45352</v>
       </c>
       <c r="B61">
@@ -2530,7 +2556,7 @@
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>45383</v>
       </c>
       <c r="B62">
@@ -2562,7 +2588,7 @@
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>45413</v>
       </c>
       <c r="B63">
@@ -2594,7 +2620,7 @@
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <v>45444</v>
       </c>
       <c r="B64">
@@ -2626,7 +2652,7 @@
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>45474</v>
       </c>
       <c r="B65">
@@ -2658,7 +2684,7 @@
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <v>45505</v>
       </c>
       <c r="B66">
@@ -2690,7 +2716,7 @@
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="1">
+      <c r="A67" s="2">
         <v>45536</v>
       </c>
       <c r="B67">
@@ -2722,7 +2748,7 @@
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <v>45566</v>
       </c>
       <c r="B68">
@@ -2754,7 +2780,7 @@
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>45597</v>
       </c>
       <c r="B69">
@@ -2786,7 +2812,7 @@
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>45627</v>
       </c>
       <c r="B70">
@@ -2818,7 +2844,7 @@
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="1">
+      <c r="A71" s="2">
         <v>45658</v>
       </c>
       <c r="B71">
@@ -2850,7 +2876,7 @@
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="1">
+      <c r="A72" s="2">
         <v>45689</v>
       </c>
       <c r="B72">
@@ -2882,7 +2908,7 @@
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="1">
+      <c r="A73" s="2">
         <v>45717</v>
       </c>
       <c r="B73">
@@ -2914,7 +2940,7 @@
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="1">
+      <c r="A74" s="2">
         <v>45748</v>
       </c>
       <c r="B74">
@@ -2946,7 +2972,7 @@
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="1">
+      <c r="A75" s="2">
         <v>45778</v>
       </c>
       <c r="B75">
@@ -2978,7 +3004,7 @@
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="1">
+      <c r="A76" s="2">
         <v>45809</v>
       </c>
       <c r="B76">
@@ -3010,7 +3036,7 @@
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="1">
+      <c r="A77" s="2">
         <v>45839</v>
       </c>
       <c r="B77">
@@ -3042,7 +3068,7 @@
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="1">
+      <c r="A78" s="2">
         <v>45870</v>
       </c>
       <c r="B78">
@@ -3074,7 +3100,7 @@
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="1">
+      <c r="A79" s="2">
         <v>45901</v>
       </c>
       <c r="B79">
@@ -3106,7 +3132,7 @@
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <v>45931</v>
       </c>
       <c r="B80">
@@ -3138,7 +3164,7 @@
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>45962</v>
       </c>
       <c r="B81">
@@ -3170,7 +3196,7 @@
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <v>45992</v>
       </c>
       <c r="B82">
@@ -3202,7 +3228,7 @@
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <v>46023</v>
       </c>
       <c r="B83">
@@ -3234,7 +3260,7 @@
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <v>46054</v>
       </c>
       <c r="B84">
@@ -3266,7 +3292,7 @@
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <v>46082</v>
       </c>
       <c r="B85">
@@ -3298,7 +3324,7 @@
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <v>46113</v>
       </c>
       <c r="B86">
@@ -3330,7 +3356,7 @@
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <v>46143</v>
       </c>
       <c r="B87">
@@ -3362,7 +3388,7 @@
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>46174</v>
       </c>
       <c r="B88">
@@ -3394,7 +3420,7 @@
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <v>46204</v>
       </c>
       <c r="B89">
@@ -3426,7 +3452,7 @@
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <v>46235</v>
       </c>
       <c r="B90">
@@ -3458,7 +3484,7 @@
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <v>46266</v>
       </c>
       <c r="B91">
@@ -3490,7 +3516,7 @@
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <v>44927</v>
       </c>
       <c r="B92">
@@ -3522,7 +3548,7 @@
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>44958</v>
       </c>
       <c r="B93">
@@ -3554,7 +3580,7 @@
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="1">
+      <c r="A94" s="2">
         <v>44986</v>
       </c>
       <c r="B94">
@@ -3586,7 +3612,7 @@
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="1">
+      <c r="A95" s="2">
         <v>45017</v>
       </c>
       <c r="B95">
@@ -3618,7 +3644,7 @@
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="1">
+      <c r="A96" s="2">
         <v>45047</v>
       </c>
       <c r="B96">
@@ -3650,7 +3676,7 @@
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="1">
+      <c r="A97" s="2">
         <v>45078</v>
       </c>
       <c r="B97">
@@ -3682,7 +3708,7 @@
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>45108</v>
       </c>
       <c r="B98">
@@ -3714,7 +3740,7 @@
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="1">
+      <c r="A99" s="2">
         <v>45139</v>
       </c>
       <c r="B99">
@@ -3746,7 +3772,7 @@
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="1">
+      <c r="A100" s="2">
         <v>45170</v>
       </c>
       <c r="B100">
@@ -3778,7 +3804,7 @@
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="1">
+      <c r="A101" s="2">
         <v>45200</v>
       </c>
       <c r="B101">
@@ -3810,7 +3836,7 @@
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="1">
+      <c r="A102" s="2">
         <v>45231</v>
       </c>
       <c r="B102">
@@ -3842,7 +3868,7 @@
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="1">
+      <c r="A103" s="2">
         <v>45261</v>
       </c>
       <c r="B103">
@@ -3874,7 +3900,7 @@
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="1">
+      <c r="A104" s="2">
         <v>45292</v>
       </c>
       <c r="B104">
@@ -3906,7 +3932,7 @@
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="1">
+      <c r="A105" s="2">
         <v>45323</v>
       </c>
       <c r="B105">
@@ -3938,7 +3964,7 @@
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="1">
+      <c r="A106" s="2">
         <v>45352</v>
       </c>
       <c r="B106">
@@ -3970,7 +3996,7 @@
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="1">
+      <c r="A107" s="2">
         <v>45383</v>
       </c>
       <c r="B107">
@@ -4002,7 +4028,7 @@
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="1">
+      <c r="A108" s="2">
         <v>45413</v>
       </c>
       <c r="B108">
@@ -4034,7 +4060,7 @@
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="1">
+      <c r="A109" s="2">
         <v>45444</v>
       </c>
       <c r="B109">
@@ -4066,7 +4092,7 @@
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="1">
+      <c r="A110" s="2">
         <v>45474</v>
       </c>
       <c r="B110">
@@ -4098,7 +4124,7 @@
       </c>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="1">
+      <c r="A111" s="2">
         <v>45505</v>
       </c>
       <c r="B111">
@@ -4130,7 +4156,7 @@
       </c>
     </row>
     <row r="112" spans="1:10">
-      <c r="A112" s="1">
+      <c r="A112" s="2">
         <v>45536</v>
       </c>
       <c r="B112">
@@ -4162,7 +4188,7 @@
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="1">
+      <c r="A113" s="2">
         <v>45566</v>
       </c>
       <c r="B113">
@@ -4194,7 +4220,7 @@
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="1">
+      <c r="A114" s="2">
         <v>45597</v>
       </c>
       <c r="B114">
@@ -4226,7 +4252,7 @@
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="1">
+      <c r="A115" s="2">
         <v>45627</v>
       </c>
       <c r="B115">
@@ -4258,7 +4284,7 @@
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="1">
+      <c r="A116" s="2">
         <v>45658</v>
       </c>
       <c r="B116">
@@ -4290,7 +4316,7 @@
       </c>
     </row>
     <row r="117" spans="1:10">
-      <c r="A117" s="1">
+      <c r="A117" s="2">
         <v>45689</v>
       </c>
       <c r="B117">
@@ -4322,7 +4348,7 @@
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="1">
+      <c r="A118" s="2">
         <v>45717</v>
       </c>
       <c r="B118">
@@ -4354,7 +4380,7 @@
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="1">
+      <c r="A119" s="2">
         <v>45748</v>
       </c>
       <c r="B119">
@@ -4386,7 +4412,7 @@
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="1">
+      <c r="A120" s="2">
         <v>45778</v>
       </c>
       <c r="B120">
@@ -4418,7 +4444,7 @@
       </c>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" s="1">
+      <c r="A121" s="2">
         <v>45809</v>
       </c>
       <c r="B121">
@@ -4450,7 +4476,7 @@
       </c>
     </row>
     <row r="122" spans="1:10">
-      <c r="A122" s="1">
+      <c r="A122" s="2">
         <v>45839</v>
       </c>
       <c r="B122">
@@ -4482,7 +4508,7 @@
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="1">
+      <c r="A123" s="2">
         <v>45870</v>
       </c>
       <c r="B123">
@@ -4514,7 +4540,7 @@
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="1">
+      <c r="A124" s="2">
         <v>45901</v>
       </c>
       <c r="B124">
@@ -4546,7 +4572,7 @@
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="1">
+      <c r="A125" s="2">
         <v>45931</v>
       </c>
       <c r="B125">
@@ -4578,7 +4604,7 @@
       </c>
     </row>
     <row r="126" spans="1:10">
-      <c r="A126" s="1">
+      <c r="A126" s="2">
         <v>45962</v>
       </c>
       <c r="B126">
@@ -4610,7 +4636,7 @@
       </c>
     </row>
     <row r="127" spans="1:10">
-      <c r="A127" s="1">
+      <c r="A127" s="2">
         <v>45992</v>
       </c>
       <c r="B127">
@@ -4642,7 +4668,7 @@
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="A128" s="1">
+      <c r="A128" s="2">
         <v>46023</v>
       </c>
       <c r="B128">
@@ -4674,7 +4700,7 @@
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" s="1">
+      <c r="A129" s="2">
         <v>46054</v>
       </c>
       <c r="B129">
@@ -4706,7 +4732,7 @@
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="1">
+      <c r="A130" s="2">
         <v>46082</v>
       </c>
       <c r="B130">
@@ -4738,7 +4764,7 @@
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" s="1">
+      <c r="A131" s="2">
         <v>46113</v>
       </c>
       <c r="B131">
@@ -4770,7 +4796,7 @@
       </c>
     </row>
     <row r="132" spans="1:10">
-      <c r="A132" s="1">
+      <c r="A132" s="2">
         <v>46143</v>
       </c>
       <c r="B132">
@@ -4802,7 +4828,7 @@
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" s="1">
+      <c r="A133" s="2">
         <v>46174</v>
       </c>
       <c r="B133">
@@ -4834,7 +4860,7 @@
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="1">
+      <c r="A134" s="2">
         <v>46204</v>
       </c>
       <c r="B134">
@@ -4866,7 +4892,7 @@
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="A135" s="1">
+      <c r="A135" s="2">
         <v>46235</v>
       </c>
       <c r="B135">
@@ -4898,7 +4924,7 @@
       </c>
     </row>
     <row r="136" spans="1:10">
-      <c r="A136" s="1">
+      <c r="A136" s="2">
         <v>46266</v>
       </c>
       <c r="B136">
@@ -4930,7 +4956,7 @@
       </c>
     </row>
     <row r="137" spans="1:10">
-      <c r="A137" s="1">
+      <c r="A137" s="2">
         <v>44927</v>
       </c>
       <c r="B137">
@@ -4962,7 +4988,7 @@
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="1">
+      <c r="A138" s="2">
         <v>44958</v>
       </c>
       <c r="B138">
@@ -4994,7 +5020,7 @@
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="1">
+      <c r="A139" s="2">
         <v>44986</v>
       </c>
       <c r="B139">
@@ -5026,7 +5052,7 @@
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" s="1">
+      <c r="A140" s="2">
         <v>45017</v>
       </c>
       <c r="B140">
@@ -5058,7 +5084,7 @@
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" s="1">
+      <c r="A141" s="2">
         <v>45047</v>
       </c>
       <c r="B141">
@@ -5090,7 +5116,7 @@
       </c>
     </row>
     <row r="142" spans="1:10">
-      <c r="A142" s="1">
+      <c r="A142" s="2">
         <v>45078</v>
       </c>
       <c r="B142">
@@ -5122,7 +5148,7 @@
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="1">
+      <c r="A143" s="2">
         <v>45108</v>
       </c>
       <c r="B143">
@@ -5154,7 +5180,7 @@
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" s="1">
+      <c r="A144" s="2">
         <v>45139</v>
       </c>
       <c r="B144">
@@ -5186,7 +5212,7 @@
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" s="1">
+      <c r="A145" s="2">
         <v>45170</v>
       </c>
       <c r="B145">
@@ -5218,7 +5244,7 @@
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="1">
+      <c r="A146" s="2">
         <v>45200</v>
       </c>
       <c r="B146">
@@ -5250,7 +5276,7 @@
       </c>
     </row>
     <row r="147" spans="1:10">
-      <c r="A147" s="1">
+      <c r="A147" s="2">
         <v>45231</v>
       </c>
       <c r="B147">
@@ -5282,7 +5308,7 @@
       </c>
     </row>
     <row r="148" spans="1:10">
-      <c r="A148" s="1">
+      <c r="A148" s="2">
         <v>45261</v>
       </c>
       <c r="B148">
@@ -5314,7 +5340,7 @@
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" s="1">
+      <c r="A149" s="2">
         <v>45292</v>
       </c>
       <c r="B149">
@@ -5346,7 +5372,7 @@
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" s="1">
+      <c r="A150" s="2">
         <v>45323</v>
       </c>
       <c r="B150">
@@ -5378,7 +5404,7 @@
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="1">
+      <c r="A151" s="2">
         <v>45352</v>
       </c>
       <c r="B151">
@@ -5410,7 +5436,7 @@
       </c>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" s="1">
+      <c r="A152" s="2">
         <v>45383</v>
       </c>
       <c r="B152">
@@ -5442,7 +5468,7 @@
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="1">
+      <c r="A153" s="2">
         <v>45413</v>
       </c>
       <c r="B153">
@@ -5474,7 +5500,7 @@
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="1">
+      <c r="A154" s="2">
         <v>45444</v>
       </c>
       <c r="B154">
@@ -5506,7 +5532,7 @@
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="1">
+      <c r="A155" s="2">
         <v>45474</v>
       </c>
       <c r="B155">
@@ -5538,7 +5564,7 @@
       </c>
     </row>
     <row r="156" spans="1:10">
-      <c r="A156" s="1">
+      <c r="A156" s="2">
         <v>45505</v>
       </c>
       <c r="B156">
@@ -5570,7 +5596,7 @@
       </c>
     </row>
     <row r="157" spans="1:10">
-      <c r="A157" s="1">
+      <c r="A157" s="2">
         <v>45536</v>
       </c>
       <c r="B157">
@@ -5602,7 +5628,7 @@
       </c>
     </row>
     <row r="158" spans="1:10">
-      <c r="A158" s="1">
+      <c r="A158" s="2">
         <v>45566</v>
       </c>
       <c r="B158">
@@ -5634,7 +5660,7 @@
       </c>
     </row>
     <row r="159" spans="1:10">
-      <c r="A159" s="1">
+      <c r="A159" s="2">
         <v>45597</v>
       </c>
       <c r="B159">
@@ -5666,7 +5692,7 @@
       </c>
     </row>
     <row r="160" spans="1:10">
-      <c r="A160" s="1">
+      <c r="A160" s="2">
         <v>45627</v>
       </c>
       <c r="B160">
@@ -5698,7 +5724,7 @@
       </c>
     </row>
     <row r="161" spans="1:10">
-      <c r="A161" s="1">
+      <c r="A161" s="2">
         <v>45658</v>
       </c>
       <c r="B161">
@@ -5730,7 +5756,7 @@
       </c>
     </row>
     <row r="162" spans="1:10">
-      <c r="A162" s="1">
+      <c r="A162" s="2">
         <v>45689</v>
       </c>
       <c r="B162">
@@ -5762,7 +5788,7 @@
       </c>
     </row>
     <row r="163" spans="1:10">
-      <c r="A163" s="1">
+      <c r="A163" s="2">
         <v>45717</v>
       </c>
       <c r="B163">
@@ -5794,7 +5820,7 @@
       </c>
     </row>
     <row r="164" spans="1:10">
-      <c r="A164" s="1">
+      <c r="A164" s="2">
         <v>45748</v>
       </c>
       <c r="B164">
@@ -5826,7 +5852,7 @@
       </c>
     </row>
     <row r="165" spans="1:10">
-      <c r="A165" s="1">
+      <c r="A165" s="2">
         <v>45778</v>
       </c>
       <c r="B165">
@@ -5858,7 +5884,7 @@
       </c>
     </row>
     <row r="166" spans="1:10">
-      <c r="A166" s="1">
+      <c r="A166" s="2">
         <v>45809</v>
       </c>
       <c r="B166">
@@ -5890,7 +5916,7 @@
       </c>
     </row>
     <row r="167" spans="1:10">
-      <c r="A167" s="1">
+      <c r="A167" s="2">
         <v>45839</v>
       </c>
       <c r="B167">
@@ -5922,7 +5948,7 @@
       </c>
     </row>
     <row r="168" spans="1:10">
-      <c r="A168" s="1">
+      <c r="A168" s="2">
         <v>45870</v>
       </c>
       <c r="B168">
@@ -5954,7 +5980,7 @@
       </c>
     </row>
     <row r="169" spans="1:10">
-      <c r="A169" s="1">
+      <c r="A169" s="2">
         <v>45901</v>
       </c>
       <c r="B169">
@@ -5986,7 +6012,7 @@
       </c>
     </row>
     <row r="170" spans="1:10">
-      <c r="A170" s="1">
+      <c r="A170" s="2">
         <v>45931</v>
       </c>
       <c r="B170">
@@ -6018,7 +6044,7 @@
       </c>
     </row>
     <row r="171" spans="1:10">
-      <c r="A171" s="1">
+      <c r="A171" s="2">
         <v>45962</v>
       </c>
       <c r="B171">
@@ -6050,7 +6076,7 @@
       </c>
     </row>
     <row r="172" spans="1:10">
-      <c r="A172" s="1">
+      <c r="A172" s="2">
         <v>45992</v>
       </c>
       <c r="B172">
@@ -6082,7 +6108,7 @@
       </c>
     </row>
     <row r="173" spans="1:10">
-      <c r="A173" s="1">
+      <c r="A173" s="2">
         <v>46023</v>
       </c>
       <c r="B173">
@@ -6114,7 +6140,7 @@
       </c>
     </row>
     <row r="174" spans="1:10">
-      <c r="A174" s="1">
+      <c r="A174" s="2">
         <v>46054</v>
       </c>
       <c r="B174">
@@ -6146,7 +6172,7 @@
       </c>
     </row>
     <row r="175" spans="1:10">
-      <c r="A175" s="1">
+      <c r="A175" s="2">
         <v>46082</v>
       </c>
       <c r="B175">
@@ -6178,7 +6204,7 @@
       </c>
     </row>
     <row r="176" spans="1:10">
-      <c r="A176" s="1">
+      <c r="A176" s="2">
         <v>46113</v>
       </c>
       <c r="B176">
@@ -6210,7 +6236,7 @@
       </c>
     </row>
     <row r="177" spans="1:10">
-      <c r="A177" s="1">
+      <c r="A177" s="2">
         <v>46143</v>
       </c>
       <c r="B177">
@@ -6242,7 +6268,7 @@
       </c>
     </row>
     <row r="178" spans="1:10">
-      <c r="A178" s="1">
+      <c r="A178" s="2">
         <v>46174</v>
       </c>
       <c r="B178">
@@ -6274,7 +6300,7 @@
       </c>
     </row>
     <row r="179" spans="1:10">
-      <c r="A179" s="1">
+      <c r="A179" s="2">
         <v>46204</v>
       </c>
       <c r="B179">
@@ -6306,7 +6332,7 @@
       </c>
     </row>
     <row r="180" spans="1:10">
-      <c r="A180" s="1">
+      <c r="A180" s="2">
         <v>46235</v>
       </c>
       <c r="B180">
@@ -6338,7 +6364,7 @@
       </c>
     </row>
     <row r="181" spans="1:10">
-      <c r="A181" s="1">
+      <c r="A181" s="2">
         <v>46266</v>
       </c>
       <c r="B181">
@@ -6370,7 +6396,7 @@
       </c>
     </row>
     <row r="182" spans="1:10">
-      <c r="A182" s="1">
+      <c r="A182" s="2">
         <v>44927</v>
       </c>
       <c r="B182">
@@ -6402,7 +6428,7 @@
       </c>
     </row>
     <row r="183" spans="1:10">
-      <c r="A183" s="1">
+      <c r="A183" s="2">
         <v>44958</v>
       </c>
       <c r="B183">
@@ -6434,7 +6460,7 @@
       </c>
     </row>
     <row r="184" spans="1:10">
-      <c r="A184" s="1">
+      <c r="A184" s="2">
         <v>44986</v>
       </c>
       <c r="B184">
@@ -6466,7 +6492,7 @@
       </c>
     </row>
     <row r="185" spans="1:10">
-      <c r="A185" s="1">
+      <c r="A185" s="2">
         <v>45017</v>
       </c>
       <c r="B185">
@@ -6498,7 +6524,7 @@
       </c>
     </row>
     <row r="186" spans="1:10">
-      <c r="A186" s="1">
+      <c r="A186" s="2">
         <v>45047</v>
       </c>
       <c r="B186">
@@ -6530,7 +6556,7 @@
       </c>
     </row>
     <row r="187" spans="1:10">
-      <c r="A187" s="1">
+      <c r="A187" s="2">
         <v>45078</v>
       </c>
       <c r="B187">
@@ -6562,7 +6588,7 @@
       </c>
     </row>
     <row r="188" spans="1:10">
-      <c r="A188" s="1">
+      <c r="A188" s="2">
         <v>45108</v>
       </c>
       <c r="B188">
@@ -6594,7 +6620,7 @@
       </c>
     </row>
     <row r="189" spans="1:10">
-      <c r="A189" s="1">
+      <c r="A189" s="2">
         <v>45139</v>
       </c>
       <c r="B189">
@@ -6626,7 +6652,7 @@
       </c>
     </row>
     <row r="190" spans="1:10">
-      <c r="A190" s="1">
+      <c r="A190" s="2">
         <v>45170</v>
       </c>
       <c r="B190">
@@ -6658,7 +6684,7 @@
       </c>
     </row>
     <row r="191" spans="1:10">
-      <c r="A191" s="1">
+      <c r="A191" s="2">
         <v>45200</v>
       </c>
       <c r="B191">
@@ -6690,7 +6716,7 @@
       </c>
     </row>
     <row r="192" spans="1:10">
-      <c r="A192" s="1">
+      <c r="A192" s="2">
         <v>45231</v>
       </c>
       <c r="B192">
@@ -6722,7 +6748,7 @@
       </c>
     </row>
     <row r="193" spans="1:10">
-      <c r="A193" s="1">
+      <c r="A193" s="2">
         <v>45261</v>
       </c>
       <c r="B193">
@@ -6754,7 +6780,7 @@
       </c>
     </row>
     <row r="194" spans="1:10">
-      <c r="A194" s="1">
+      <c r="A194" s="2">
         <v>45292</v>
       </c>
       <c r="B194">
@@ -6786,7 +6812,7 @@
       </c>
     </row>
     <row r="195" spans="1:10">
-      <c r="A195" s="1">
+      <c r="A195" s="2">
         <v>45323</v>
       </c>
       <c r="B195">
@@ -6818,7 +6844,7 @@
       </c>
     </row>
     <row r="196" spans="1:10">
-      <c r="A196" s="1">
+      <c r="A196" s="2">
         <v>45352</v>
       </c>
       <c r="B196">
@@ -6850,7 +6876,7 @@
       </c>
     </row>
     <row r="197" spans="1:10">
-      <c r="A197" s="1">
+      <c r="A197" s="2">
         <v>45383</v>
       </c>
       <c r="B197">
@@ -6882,7 +6908,7 @@
       </c>
     </row>
     <row r="198" spans="1:10">
-      <c r="A198" s="1">
+      <c r="A198" s="2">
         <v>45413</v>
       </c>
       <c r="B198">
@@ -6914,7 +6940,7 @@
       </c>
     </row>
     <row r="199" spans="1:10">
-      <c r="A199" s="1">
+      <c r="A199" s="2">
         <v>45444</v>
       </c>
       <c r="B199">
@@ -6946,7 +6972,7 @@
       </c>
     </row>
     <row r="200" spans="1:10">
-      <c r="A200" s="1">
+      <c r="A200" s="2">
         <v>45474</v>
       </c>
       <c r="B200">
@@ -6978,7 +7004,7 @@
       </c>
     </row>
     <row r="201" spans="1:10">
-      <c r="A201" s="1">
+      <c r="A201" s="2">
         <v>45505</v>
       </c>
       <c r="B201">
@@ -7010,7 +7036,7 @@
       </c>
     </row>
     <row r="202" spans="1:10">
-      <c r="A202" s="1">
+      <c r="A202" s="2">
         <v>45536</v>
       </c>
       <c r="B202">
@@ -7042,7 +7068,7 @@
       </c>
     </row>
     <row r="203" spans="1:10">
-      <c r="A203" s="1">
+      <c r="A203" s="2">
         <v>45566</v>
       </c>
       <c r="B203">
@@ -7074,7 +7100,7 @@
       </c>
     </row>
     <row r="204" spans="1:10">
-      <c r="A204" s="1">
+      <c r="A204" s="2">
         <v>45597</v>
       </c>
       <c r="B204">
@@ -7106,7 +7132,7 @@
       </c>
     </row>
     <row r="205" spans="1:10">
-      <c r="A205" s="1">
+      <c r="A205" s="2">
         <v>45627</v>
       </c>
       <c r="B205">
@@ -7138,7 +7164,7 @@
       </c>
     </row>
     <row r="206" spans="1:10">
-      <c r="A206" s="1">
+      <c r="A206" s="2">
         <v>45658</v>
       </c>
       <c r="B206">
@@ -7170,7 +7196,7 @@
       </c>
     </row>
     <row r="207" spans="1:10">
-      <c r="A207" s="1">
+      <c r="A207" s="2">
         <v>45689</v>
       </c>
       <c r="B207">
@@ -7202,7 +7228,7 @@
       </c>
     </row>
     <row r="208" spans="1:10">
-      <c r="A208" s="1">
+      <c r="A208" s="2">
         <v>45717</v>
       </c>
       <c r="B208">
@@ -7234,7 +7260,7 @@
       </c>
     </row>
     <row r="209" spans="1:10">
-      <c r="A209" s="1">
+      <c r="A209" s="2">
         <v>45748</v>
       </c>
       <c r="B209">
@@ -7266,7 +7292,7 @@
       </c>
     </row>
     <row r="210" spans="1:10">
-      <c r="A210" s="1">
+      <c r="A210" s="2">
         <v>45778</v>
       </c>
       <c r="B210">
@@ -7298,7 +7324,7 @@
       </c>
     </row>
     <row r="211" spans="1:10">
-      <c r="A211" s="1">
+      <c r="A211" s="2">
         <v>45809</v>
       </c>
       <c r="B211">
@@ -7330,7 +7356,7 @@
       </c>
     </row>
     <row r="212" spans="1:10">
-      <c r="A212" s="1">
+      <c r="A212" s="2">
         <v>45839</v>
       </c>
       <c r="B212">
@@ -7362,7 +7388,7 @@
       </c>
     </row>
     <row r="213" spans="1:10">
-      <c r="A213" s="1">
+      <c r="A213" s="2">
         <v>45870</v>
       </c>
       <c r="B213">
@@ -7394,7 +7420,7 @@
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="A214" s="1">
+      <c r="A214" s="2">
         <v>45901</v>
       </c>
       <c r="B214">
@@ -7426,7 +7452,7 @@
       </c>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" s="1">
+      <c r="A215" s="2">
         <v>45931</v>
       </c>
       <c r="B215">
@@ -7458,7 +7484,7 @@
       </c>
     </row>
     <row r="216" spans="1:10">
-      <c r="A216" s="1">
+      <c r="A216" s="2">
         <v>45962</v>
       </c>
       <c r="B216">
@@ -7490,7 +7516,7 @@
       </c>
     </row>
     <row r="217" spans="1:10">
-      <c r="A217" s="1">
+      <c r="A217" s="2">
         <v>45992</v>
       </c>
       <c r="B217">
@@ -7522,7 +7548,7 @@
       </c>
     </row>
     <row r="218" spans="1:10">
-      <c r="A218" s="1">
+      <c r="A218" s="2">
         <v>46023</v>
       </c>
       <c r="B218">
@@ -7554,7 +7580,7 @@
       </c>
     </row>
     <row r="219" spans="1:10">
-      <c r="A219" s="1">
+      <c r="A219" s="2">
         <v>46054</v>
       </c>
       <c r="B219">
@@ -7586,7 +7612,7 @@
       </c>
     </row>
     <row r="220" spans="1:10">
-      <c r="A220" s="1">
+      <c r="A220" s="2">
         <v>46082</v>
       </c>
       <c r="B220">
@@ -7618,7 +7644,7 @@
       </c>
     </row>
     <row r="221" spans="1:10">
-      <c r="A221" s="1">
+      <c r="A221" s="2">
         <v>46113</v>
       </c>
       <c r="B221">
@@ -7650,7 +7676,7 @@
       </c>
     </row>
     <row r="222" spans="1:10">
-      <c r="A222" s="1">
+      <c r="A222" s="2">
         <v>46143</v>
       </c>
       <c r="B222">
@@ -7682,7 +7708,7 @@
       </c>
     </row>
     <row r="223" spans="1:10">
-      <c r="A223" s="1">
+      <c r="A223" s="2">
         <v>46174</v>
       </c>
       <c r="B223">
@@ -7714,7 +7740,7 @@
       </c>
     </row>
     <row r="224" spans="1:10">
-      <c r="A224" s="1">
+      <c r="A224" s="2">
         <v>46204</v>
       </c>
       <c r="B224">
@@ -7746,7 +7772,7 @@
       </c>
     </row>
     <row r="225" spans="1:10">
-      <c r="A225" s="1">
+      <c r="A225" s="2">
         <v>46235</v>
       </c>
       <c r="B225">
@@ -7778,7 +7804,7 @@
       </c>
     </row>
     <row r="226" spans="1:10">
-      <c r="A226" s="1">
+      <c r="A226" s="2">
         <v>46266</v>
       </c>
       <c r="B226">
@@ -7820,40 +7846,40 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
@@ -8058,46 +8084,46 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -8332,25 +8358,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -8364,7 +8390,7 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>46204</v>
       </c>
       <c r="E2">
@@ -8387,7 +8413,7 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>45839</v>
       </c>
       <c r="E3">
@@ -8410,7 +8436,7 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>45992</v>
       </c>
       <c r="E4">
@@ -8433,7 +8459,7 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>46143</v>
       </c>
       <c r="E5">
@@ -8456,7 +8482,7 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>45108</v>
       </c>
       <c r="E6">
@@ -8479,7 +8505,7 @@
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2">
         <v>45108</v>
       </c>
       <c r="E7">
@@ -8502,7 +8528,7 @@
       <c r="C8">
         <v>2</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
         <v>45078</v>
       </c>
       <c r="E8">
@@ -8525,7 +8551,7 @@
       <c r="C9">
         <v>3</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2">
         <v>45047</v>
       </c>
       <c r="E9">
@@ -8548,7 +8574,7 @@
       <c r="C10">
         <v>4</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="2">
         <v>45017</v>
       </c>
       <c r="E10">
@@ -8571,7 +8597,7 @@
       <c r="C11">
         <v>5</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2">
         <v>44927</v>
       </c>
       <c r="E11">
@@ -8594,7 +8620,7 @@
       <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="2">
         <v>45108</v>
       </c>
       <c r="E12">
@@ -8617,7 +8643,7 @@
       <c r="C13">
         <v>2</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="2">
         <v>45839</v>
       </c>
       <c r="E13">
@@ -8640,7 +8666,7 @@
       <c r="C14">
         <v>3</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="2">
         <v>46204</v>
       </c>
       <c r="E14">
@@ -8663,7 +8689,7 @@
       <c r="C15">
         <v>4</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="2">
         <v>45078</v>
       </c>
       <c r="E15">
@@ -8686,7 +8712,7 @@
       <c r="C16">
         <v>5</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2">
         <v>45261</v>
       </c>
       <c r="E16">
@@ -8709,7 +8735,7 @@
       <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="2">
         <v>44927</v>
       </c>
       <c r="E17">
@@ -8732,7 +8758,7 @@
       <c r="C18">
         <v>2</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="2">
         <v>45839</v>
       </c>
       <c r="E18">
@@ -8755,7 +8781,7 @@
       <c r="C19">
         <v>3</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="2">
         <v>46204</v>
       </c>
       <c r="E19">
@@ -8778,7 +8804,7 @@
       <c r="C20">
         <v>4</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="2">
         <v>45992</v>
       </c>
       <c r="E20">
@@ -8801,7 +8827,7 @@
       <c r="C21">
         <v>5</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="2">
         <v>46174</v>
       </c>
       <c r="E21">
@@ -8824,7 +8850,7 @@
       <c r="C22">
         <v>1</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="2">
         <v>46235</v>
       </c>
       <c r="E22">
@@ -8847,7 +8873,7 @@
       <c r="C23">
         <v>2</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="2">
         <v>45839</v>
       </c>
       <c r="E23">
@@ -8870,7 +8896,7 @@
       <c r="C24">
         <v>3</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="2">
         <v>45870</v>
       </c>
       <c r="E24">
@@ -8893,7 +8919,7 @@
       <c r="C25">
         <v>4</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="2">
         <v>45809</v>
       </c>
       <c r="E25">
@@ -8916,7 +8942,7 @@
       <c r="C26">
         <v>5</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="2">
         <v>45352</v>
       </c>
       <c r="E26">
@@ -8940,31 +8966,31 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
@@ -9124,39 +9150,39 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>44927</v>
       </c>
       <c r="B2">
@@ -9188,7 +9214,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>44958</v>
       </c>
       <c r="B3">
@@ -9220,7 +9246,7 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>44986</v>
       </c>
       <c r="B4">
@@ -9252,7 +9278,7 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>45017</v>
       </c>
       <c r="B5">
@@ -9284,7 +9310,7 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>45047</v>
       </c>
       <c r="B6">
@@ -9316,7 +9342,7 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>45078</v>
       </c>
       <c r="B7">
@@ -9348,7 +9374,7 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>45108</v>
       </c>
       <c r="B8">
@@ -9380,7 +9406,7 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>45139</v>
       </c>
       <c r="B9">
@@ -9412,7 +9438,7 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>45170</v>
       </c>
       <c r="B10">
@@ -9444,7 +9470,7 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>45200</v>
       </c>
       <c r="B11">
@@ -9476,7 +9502,7 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>45231</v>
       </c>
       <c r="B12">
@@ -9508,7 +9534,7 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>45261</v>
       </c>
       <c r="B13">
@@ -9540,7 +9566,7 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>45292</v>
       </c>
       <c r="B14">
@@ -9572,7 +9598,7 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>45323</v>
       </c>
       <c r="B15">
@@ -9604,7 +9630,7 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>45352</v>
       </c>
       <c r="B16">
@@ -9636,7 +9662,7 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>45383</v>
       </c>
       <c r="B17">
@@ -9668,7 +9694,7 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>45413</v>
       </c>
       <c r="B18">
@@ -9700,7 +9726,7 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>45444</v>
       </c>
       <c r="B19">
@@ -9732,7 +9758,7 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>45474</v>
       </c>
       <c r="B20">
@@ -9764,7 +9790,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>45505</v>
       </c>
       <c r="B21">
@@ -9796,7 +9822,7 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>45536</v>
       </c>
       <c r="B22">
@@ -9828,7 +9854,7 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>45566</v>
       </c>
       <c r="B23">
@@ -9860,7 +9886,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>45597</v>
       </c>
       <c r="B24">
@@ -9892,7 +9918,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>45627</v>
       </c>
       <c r="B25">
@@ -9924,7 +9950,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>45658</v>
       </c>
       <c r="B26">
@@ -9956,7 +9982,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>45689</v>
       </c>
       <c r="B27">
@@ -9988,7 +10014,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>45717</v>
       </c>
       <c r="B28">
@@ -10020,7 +10046,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>45748</v>
       </c>
       <c r="B29">
@@ -10052,7 +10078,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>45778</v>
       </c>
       <c r="B30">
@@ -10084,7 +10110,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>45809</v>
       </c>
       <c r="B31">
@@ -10116,7 +10142,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>45839</v>
       </c>
       <c r="B32">
@@ -10148,7 +10174,7 @@
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>45870</v>
       </c>
       <c r="B33">
@@ -10180,7 +10206,7 @@
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>45901</v>
       </c>
       <c r="B34">
@@ -10212,7 +10238,7 @@
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>45931</v>
       </c>
       <c r="B35">
@@ -10244,7 +10270,7 @@
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>45962</v>
       </c>
       <c r="B36">
@@ -10276,7 +10302,7 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>45992</v>
       </c>
       <c r="B37">
@@ -10308,7 +10334,7 @@
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>46023</v>
       </c>
       <c r="B38">
@@ -10340,7 +10366,7 @@
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>46054</v>
       </c>
       <c r="B39">
@@ -10372,7 +10398,7 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>46082</v>
       </c>
       <c r="B40">
@@ -10404,7 +10430,7 @@
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>46113</v>
       </c>
       <c r="B41">
@@ -10436,7 +10462,7 @@
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>46143</v>
       </c>
       <c r="B42">
@@ -10468,7 +10494,7 @@
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <v>46174</v>
       </c>
       <c r="B43">
@@ -10500,7 +10526,7 @@
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>46204</v>
       </c>
       <c r="B44">
@@ -10532,7 +10558,7 @@
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>46235</v>
       </c>
       <c r="B45">
@@ -10564,7 +10590,7 @@
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>46266</v>
       </c>
       <c r="B46">
@@ -10596,7 +10622,7 @@
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <v>44927</v>
       </c>
       <c r="B47">
@@ -10628,7 +10654,7 @@
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>44958</v>
       </c>
       <c r="B48">
@@ -10660,7 +10686,7 @@
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>44986</v>
       </c>
       <c r="B49">
@@ -10692,7 +10718,7 @@
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>45017</v>
       </c>
       <c r="B50">
@@ -10724,7 +10750,7 @@
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="1">
+      <c r="A51" s="2">
         <v>45047</v>
       </c>
       <c r="B51">
@@ -10756,7 +10782,7 @@
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>45078</v>
       </c>
       <c r="B52">
@@ -10788,7 +10814,7 @@
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>45108</v>
       </c>
       <c r="B53">
@@ -10820,7 +10846,7 @@
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>45139</v>
       </c>
       <c r="B54">
@@ -10852,7 +10878,7 @@
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>45170</v>
       </c>
       <c r="B55">
@@ -10884,7 +10910,7 @@
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>45200</v>
       </c>
       <c r="B56">
@@ -10916,7 +10942,7 @@
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>45231</v>
       </c>
       <c r="B57">
@@ -10948,7 +10974,7 @@
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>45261</v>
       </c>
       <c r="B58">
@@ -10980,7 +11006,7 @@
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>45292</v>
       </c>
       <c r="B59">
@@ -11012,7 +11038,7 @@
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>45323</v>
       </c>
       <c r="B60">
@@ -11044,7 +11070,7 @@
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>45352</v>
       </c>
       <c r="B61">
@@ -11076,7 +11102,7 @@
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>45383</v>
       </c>
       <c r="B62">
@@ -11108,7 +11134,7 @@
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>45413</v>
       </c>
       <c r="B63">
@@ -11140,7 +11166,7 @@
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <v>45444</v>
       </c>
       <c r="B64">
@@ -11172,7 +11198,7 @@
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>45474</v>
       </c>
       <c r="B65">
@@ -11204,7 +11230,7 @@
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <v>45505</v>
       </c>
       <c r="B66">
@@ -11236,7 +11262,7 @@
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="1">
+      <c r="A67" s="2">
         <v>45536</v>
       </c>
       <c r="B67">
@@ -11268,7 +11294,7 @@
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <v>45566</v>
       </c>
       <c r="B68">
@@ -11300,7 +11326,7 @@
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>45597</v>
       </c>
       <c r="B69">
@@ -11332,7 +11358,7 @@
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>45627</v>
       </c>
       <c r="B70">
@@ -11364,7 +11390,7 @@
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="1">
+      <c r="A71" s="2">
         <v>45658</v>
       </c>
       <c r="B71">
@@ -11396,7 +11422,7 @@
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="1">
+      <c r="A72" s="2">
         <v>45689</v>
       </c>
       <c r="B72">
@@ -11428,7 +11454,7 @@
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="1">
+      <c r="A73" s="2">
         <v>45717</v>
       </c>
       <c r="B73">
@@ -11460,7 +11486,7 @@
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="1">
+      <c r="A74" s="2">
         <v>45748</v>
       </c>
       <c r="B74">
@@ -11492,7 +11518,7 @@
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="1">
+      <c r="A75" s="2">
         <v>45778</v>
       </c>
       <c r="B75">
@@ -11524,7 +11550,7 @@
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="1">
+      <c r="A76" s="2">
         <v>45809</v>
       </c>
       <c r="B76">
@@ -11556,7 +11582,7 @@
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="1">
+      <c r="A77" s="2">
         <v>45839</v>
       </c>
       <c r="B77">
@@ -11588,7 +11614,7 @@
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="1">
+      <c r="A78" s="2">
         <v>45870</v>
       </c>
       <c r="B78">
@@ -11620,7 +11646,7 @@
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="1">
+      <c r="A79" s="2">
         <v>45901</v>
       </c>
       <c r="B79">
@@ -11652,7 +11678,7 @@
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <v>45931</v>
       </c>
       <c r="B80">
@@ -11684,7 +11710,7 @@
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>45962</v>
       </c>
       <c r="B81">
@@ -11716,7 +11742,7 @@
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <v>45992</v>
       </c>
       <c r="B82">
@@ -11748,7 +11774,7 @@
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <v>46023</v>
       </c>
       <c r="B83">
@@ -11780,7 +11806,7 @@
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <v>46054</v>
       </c>
       <c r="B84">
@@ -11812,7 +11838,7 @@
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <v>46082</v>
       </c>
       <c r="B85">
@@ -11844,7 +11870,7 @@
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <v>46113</v>
       </c>
       <c r="B86">
@@ -11876,7 +11902,7 @@
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <v>46143</v>
       </c>
       <c r="B87">
@@ -11908,7 +11934,7 @@
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>46174</v>
       </c>
       <c r="B88">
@@ -11940,7 +11966,7 @@
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <v>46204</v>
       </c>
       <c r="B89">
@@ -11972,7 +11998,7 @@
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <v>46235</v>
       </c>
       <c r="B90">
@@ -12004,7 +12030,7 @@
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <v>46266</v>
       </c>
       <c r="B91">
@@ -12036,7 +12062,7 @@
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <v>44927</v>
       </c>
       <c r="B92">
@@ -12068,7 +12094,7 @@
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>44958</v>
       </c>
       <c r="B93">
@@ -12100,7 +12126,7 @@
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="1">
+      <c r="A94" s="2">
         <v>44986</v>
       </c>
       <c r="B94">
@@ -12132,7 +12158,7 @@
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="1">
+      <c r="A95" s="2">
         <v>45017</v>
       </c>
       <c r="B95">
@@ -12164,7 +12190,7 @@
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="1">
+      <c r="A96" s="2">
         <v>45047</v>
       </c>
       <c r="B96">
@@ -12196,7 +12222,7 @@
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="1">
+      <c r="A97" s="2">
         <v>45078</v>
       </c>
       <c r="B97">
@@ -12228,7 +12254,7 @@
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>45108</v>
       </c>
       <c r="B98">
@@ -12260,7 +12286,7 @@
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="1">
+      <c r="A99" s="2">
         <v>45139</v>
       </c>
       <c r="B99">
@@ -12292,7 +12318,7 @@
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="1">
+      <c r="A100" s="2">
         <v>45170</v>
       </c>
       <c r="B100">
@@ -12324,7 +12350,7 @@
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="1">
+      <c r="A101" s="2">
         <v>45200</v>
       </c>
       <c r="B101">
@@ -12356,7 +12382,7 @@
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="1">
+      <c r="A102" s="2">
         <v>45231</v>
       </c>
       <c r="B102">
@@ -12388,7 +12414,7 @@
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="1">
+      <c r="A103" s="2">
         <v>45261</v>
       </c>
       <c r="B103">
@@ -12420,7 +12446,7 @@
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="1">
+      <c r="A104" s="2">
         <v>45292</v>
       </c>
       <c r="B104">
@@ -12452,7 +12478,7 @@
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="1">
+      <c r="A105" s="2">
         <v>45323</v>
       </c>
       <c r="B105">
@@ -12484,7 +12510,7 @@
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="1">
+      <c r="A106" s="2">
         <v>45352</v>
       </c>
       <c r="B106">
@@ -12516,7 +12542,7 @@
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="1">
+      <c r="A107" s="2">
         <v>45383</v>
       </c>
       <c r="B107">
@@ -12548,7 +12574,7 @@
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="1">
+      <c r="A108" s="2">
         <v>45413</v>
       </c>
       <c r="B108">
@@ -12580,7 +12606,7 @@
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="1">
+      <c r="A109" s="2">
         <v>45444</v>
       </c>
       <c r="B109">
@@ -12612,7 +12638,7 @@
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="1">
+      <c r="A110" s="2">
         <v>45474</v>
       </c>
       <c r="B110">
@@ -12644,7 +12670,7 @@
       </c>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="1">
+      <c r="A111" s="2">
         <v>45505</v>
       </c>
       <c r="B111">
@@ -12676,7 +12702,7 @@
       </c>
     </row>
     <row r="112" spans="1:10">
-      <c r="A112" s="1">
+      <c r="A112" s="2">
         <v>45536</v>
       </c>
       <c r="B112">
@@ -12708,7 +12734,7 @@
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="1">
+      <c r="A113" s="2">
         <v>45566</v>
       </c>
       <c r="B113">
@@ -12740,7 +12766,7 @@
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="1">
+      <c r="A114" s="2">
         <v>45597</v>
       </c>
       <c r="B114">
@@ -12772,7 +12798,7 @@
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="1">
+      <c r="A115" s="2">
         <v>45627</v>
       </c>
       <c r="B115">
@@ -12804,7 +12830,7 @@
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="1">
+      <c r="A116" s="2">
         <v>45658</v>
       </c>
       <c r="B116">
@@ -12836,7 +12862,7 @@
       </c>
     </row>
     <row r="117" spans="1:10">
-      <c r="A117" s="1">
+      <c r="A117" s="2">
         <v>45689</v>
       </c>
       <c r="B117">
@@ -12868,7 +12894,7 @@
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="1">
+      <c r="A118" s="2">
         <v>45717</v>
       </c>
       <c r="B118">
@@ -12900,7 +12926,7 @@
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="1">
+      <c r="A119" s="2">
         <v>45748</v>
       </c>
       <c r="B119">
@@ -12932,7 +12958,7 @@
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="1">
+      <c r="A120" s="2">
         <v>45778</v>
       </c>
       <c r="B120">
@@ -12964,7 +12990,7 @@
       </c>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" s="1">
+      <c r="A121" s="2">
         <v>45809</v>
       </c>
       <c r="B121">
@@ -12996,7 +13022,7 @@
       </c>
     </row>
     <row r="122" spans="1:10">
-      <c r="A122" s="1">
+      <c r="A122" s="2">
         <v>45839</v>
       </c>
       <c r="B122">
@@ -13028,7 +13054,7 @@
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="1">
+      <c r="A123" s="2">
         <v>45870</v>
       </c>
       <c r="B123">
@@ -13060,7 +13086,7 @@
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="1">
+      <c r="A124" s="2">
         <v>45901</v>
       </c>
       <c r="B124">
@@ -13092,7 +13118,7 @@
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="1">
+      <c r="A125" s="2">
         <v>45931</v>
       </c>
       <c r="B125">
@@ -13124,7 +13150,7 @@
       </c>
     </row>
     <row r="126" spans="1:10">
-      <c r="A126" s="1">
+      <c r="A126" s="2">
         <v>45962</v>
       </c>
       <c r="B126">
@@ -13156,7 +13182,7 @@
       </c>
     </row>
     <row r="127" spans="1:10">
-      <c r="A127" s="1">
+      <c r="A127" s="2">
         <v>45992</v>
       </c>
       <c r="B127">
@@ -13188,7 +13214,7 @@
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="A128" s="1">
+      <c r="A128" s="2">
         <v>46023</v>
       </c>
       <c r="B128">
@@ -13220,7 +13246,7 @@
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" s="1">
+      <c r="A129" s="2">
         <v>46054</v>
       </c>
       <c r="B129">
@@ -13252,7 +13278,7 @@
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="1">
+      <c r="A130" s="2">
         <v>46082</v>
       </c>
       <c r="B130">
@@ -13284,7 +13310,7 @@
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" s="1">
+      <c r="A131" s="2">
         <v>46113</v>
       </c>
       <c r="B131">
@@ -13316,7 +13342,7 @@
       </c>
     </row>
     <row r="132" spans="1:10">
-      <c r="A132" s="1">
+      <c r="A132" s="2">
         <v>46143</v>
       </c>
       <c r="B132">
@@ -13348,7 +13374,7 @@
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" s="1">
+      <c r="A133" s="2">
         <v>46174</v>
       </c>
       <c r="B133">
@@ -13380,7 +13406,7 @@
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="1">
+      <c r="A134" s="2">
         <v>46204</v>
       </c>
       <c r="B134">
@@ -13412,7 +13438,7 @@
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="A135" s="1">
+      <c r="A135" s="2">
         <v>46235</v>
       </c>
       <c r="B135">
@@ -13444,7 +13470,7 @@
       </c>
     </row>
     <row r="136" spans="1:10">
-      <c r="A136" s="1">
+      <c r="A136" s="2">
         <v>46266</v>
       </c>
       <c r="B136">
@@ -13476,7 +13502,7 @@
       </c>
     </row>
     <row r="137" spans="1:10">
-      <c r="A137" s="1">
+      <c r="A137" s="2">
         <v>44927</v>
       </c>
       <c r="B137">
@@ -13508,7 +13534,7 @@
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="1">
+      <c r="A138" s="2">
         <v>44958</v>
       </c>
       <c r="B138">
@@ -13540,7 +13566,7 @@
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="1">
+      <c r="A139" s="2">
         <v>44986</v>
       </c>
       <c r="B139">
@@ -13572,7 +13598,7 @@
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" s="1">
+      <c r="A140" s="2">
         <v>45017</v>
       </c>
       <c r="B140">
@@ -13604,7 +13630,7 @@
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" s="1">
+      <c r="A141" s="2">
         <v>45047</v>
       </c>
       <c r="B141">
@@ -13636,7 +13662,7 @@
       </c>
     </row>
     <row r="142" spans="1:10">
-      <c r="A142" s="1">
+      <c r="A142" s="2">
         <v>45078</v>
       </c>
       <c r="B142">
@@ -13668,7 +13694,7 @@
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="1">
+      <c r="A143" s="2">
         <v>45108</v>
       </c>
       <c r="B143">
@@ -13700,7 +13726,7 @@
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" s="1">
+      <c r="A144" s="2">
         <v>45139</v>
       </c>
       <c r="B144">
@@ -13732,7 +13758,7 @@
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" s="1">
+      <c r="A145" s="2">
         <v>45170</v>
       </c>
       <c r="B145">
@@ -13764,7 +13790,7 @@
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="1">
+      <c r="A146" s="2">
         <v>45200</v>
       </c>
       <c r="B146">
@@ -13796,7 +13822,7 @@
       </c>
     </row>
     <row r="147" spans="1:10">
-      <c r="A147" s="1">
+      <c r="A147" s="2">
         <v>45231</v>
       </c>
       <c r="B147">
@@ -13828,7 +13854,7 @@
       </c>
     </row>
     <row r="148" spans="1:10">
-      <c r="A148" s="1">
+      <c r="A148" s="2">
         <v>45261</v>
       </c>
       <c r="B148">
@@ -13860,7 +13886,7 @@
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" s="1">
+      <c r="A149" s="2">
         <v>45292</v>
       </c>
       <c r="B149">
@@ -13892,7 +13918,7 @@
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" s="1">
+      <c r="A150" s="2">
         <v>45323</v>
       </c>
       <c r="B150">
@@ -13924,7 +13950,7 @@
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="1">
+      <c r="A151" s="2">
         <v>45352</v>
       </c>
       <c r="B151">
@@ -13956,7 +13982,7 @@
       </c>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" s="1">
+      <c r="A152" s="2">
         <v>45383</v>
       </c>
       <c r="B152">
@@ -13988,7 +14014,7 @@
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="1">
+      <c r="A153" s="2">
         <v>45413</v>
       </c>
       <c r="B153">
@@ -14020,7 +14046,7 @@
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="1">
+      <c r="A154" s="2">
         <v>45444</v>
       </c>
       <c r="B154">
@@ -14052,7 +14078,7 @@
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="1">
+      <c r="A155" s="2">
         <v>45474</v>
       </c>
       <c r="B155">
@@ -14084,7 +14110,7 @@
       </c>
     </row>
     <row r="156" spans="1:10">
-      <c r="A156" s="1">
+      <c r="A156" s="2">
         <v>45505</v>
       </c>
       <c r="B156">
@@ -14116,7 +14142,7 @@
       </c>
     </row>
     <row r="157" spans="1:10">
-      <c r="A157" s="1">
+      <c r="A157" s="2">
         <v>45536</v>
       </c>
       <c r="B157">
@@ -14148,7 +14174,7 @@
       </c>
     </row>
     <row r="158" spans="1:10">
-      <c r="A158" s="1">
+      <c r="A158" s="2">
         <v>45566</v>
       </c>
       <c r="B158">
@@ -14180,7 +14206,7 @@
       </c>
     </row>
     <row r="159" spans="1:10">
-      <c r="A159" s="1">
+      <c r="A159" s="2">
         <v>45597</v>
       </c>
       <c r="B159">
@@ -14212,7 +14238,7 @@
       </c>
     </row>
     <row r="160" spans="1:10">
-      <c r="A160" s="1">
+      <c r="A160" s="2">
         <v>45627</v>
       </c>
       <c r="B160">
@@ -14244,7 +14270,7 @@
       </c>
     </row>
     <row r="161" spans="1:10">
-      <c r="A161" s="1">
+      <c r="A161" s="2">
         <v>45658</v>
       </c>
       <c r="B161">
@@ -14276,7 +14302,7 @@
       </c>
     </row>
     <row r="162" spans="1:10">
-      <c r="A162" s="1">
+      <c r="A162" s="2">
         <v>45689</v>
       </c>
       <c r="B162">
@@ -14308,7 +14334,7 @@
       </c>
     </row>
     <row r="163" spans="1:10">
-      <c r="A163" s="1">
+      <c r="A163" s="2">
         <v>45717</v>
       </c>
       <c r="B163">
@@ -14340,7 +14366,7 @@
       </c>
     </row>
     <row r="164" spans="1:10">
-      <c r="A164" s="1">
+      <c r="A164" s="2">
         <v>45748</v>
       </c>
       <c r="B164">
@@ -14372,7 +14398,7 @@
       </c>
     </row>
     <row r="165" spans="1:10">
-      <c r="A165" s="1">
+      <c r="A165" s="2">
         <v>45778</v>
       </c>
       <c r="B165">
@@ -14404,7 +14430,7 @@
       </c>
     </row>
     <row r="166" spans="1:10">
-      <c r="A166" s="1">
+      <c r="A166" s="2">
         <v>45809</v>
       </c>
       <c r="B166">
@@ -14436,7 +14462,7 @@
       </c>
     </row>
     <row r="167" spans="1:10">
-      <c r="A167" s="1">
+      <c r="A167" s="2">
         <v>45839</v>
       </c>
       <c r="B167">
@@ -14468,7 +14494,7 @@
       </c>
     </row>
     <row r="168" spans="1:10">
-      <c r="A168" s="1">
+      <c r="A168" s="2">
         <v>45870</v>
       </c>
       <c r="B168">
@@ -14500,7 +14526,7 @@
       </c>
     </row>
     <row r="169" spans="1:10">
-      <c r="A169" s="1">
+      <c r="A169" s="2">
         <v>45901</v>
       </c>
       <c r="B169">
@@ -14532,7 +14558,7 @@
       </c>
     </row>
     <row r="170" spans="1:10">
-      <c r="A170" s="1">
+      <c r="A170" s="2">
         <v>45931</v>
       </c>
       <c r="B170">
@@ -14564,7 +14590,7 @@
       </c>
     </row>
     <row r="171" spans="1:10">
-      <c r="A171" s="1">
+      <c r="A171" s="2">
         <v>45962</v>
       </c>
       <c r="B171">
@@ -14596,7 +14622,7 @@
       </c>
     </row>
     <row r="172" spans="1:10">
-      <c r="A172" s="1">
+      <c r="A172" s="2">
         <v>45992</v>
       </c>
       <c r="B172">
@@ -14628,7 +14654,7 @@
       </c>
     </row>
     <row r="173" spans="1:10">
-      <c r="A173" s="1">
+      <c r="A173" s="2">
         <v>46023</v>
       </c>
       <c r="B173">
@@ -14660,7 +14686,7 @@
       </c>
     </row>
     <row r="174" spans="1:10">
-      <c r="A174" s="1">
+      <c r="A174" s="2">
         <v>46054</v>
       </c>
       <c r="B174">
@@ -14692,7 +14718,7 @@
       </c>
     </row>
     <row r="175" spans="1:10">
-      <c r="A175" s="1">
+      <c r="A175" s="2">
         <v>46082</v>
       </c>
       <c r="B175">
@@ -14724,7 +14750,7 @@
       </c>
     </row>
     <row r="176" spans="1:10">
-      <c r="A176" s="1">
+      <c r="A176" s="2">
         <v>46113</v>
       </c>
       <c r="B176">
@@ -14756,7 +14782,7 @@
       </c>
     </row>
     <row r="177" spans="1:10">
-      <c r="A177" s="1">
+      <c r="A177" s="2">
         <v>46143</v>
       </c>
       <c r="B177">
@@ -14788,7 +14814,7 @@
       </c>
     </row>
     <row r="178" spans="1:10">
-      <c r="A178" s="1">
+      <c r="A178" s="2">
         <v>46174</v>
       </c>
       <c r="B178">
@@ -14820,7 +14846,7 @@
       </c>
     </row>
     <row r="179" spans="1:10">
-      <c r="A179" s="1">
+      <c r="A179" s="2">
         <v>46204</v>
       </c>
       <c r="B179">
@@ -14852,7 +14878,7 @@
       </c>
     </row>
     <row r="180" spans="1:10">
-      <c r="A180" s="1">
+      <c r="A180" s="2">
         <v>46235</v>
       </c>
       <c r="B180">
@@ -14884,7 +14910,7 @@
       </c>
     </row>
     <row r="181" spans="1:10">
-      <c r="A181" s="1">
+      <c r="A181" s="2">
         <v>46266</v>
       </c>
       <c r="B181">
@@ -14916,7 +14942,7 @@
       </c>
     </row>
     <row r="182" spans="1:10">
-      <c r="A182" s="1">
+      <c r="A182" s="2">
         <v>44927</v>
       </c>
       <c r="B182">
@@ -14948,7 +14974,7 @@
       </c>
     </row>
     <row r="183" spans="1:10">
-      <c r="A183" s="1">
+      <c r="A183" s="2">
         <v>44958</v>
       </c>
       <c r="B183">
@@ -14980,7 +15006,7 @@
       </c>
     </row>
     <row r="184" spans="1:10">
-      <c r="A184" s="1">
+      <c r="A184" s="2">
         <v>44986</v>
       </c>
       <c r="B184">
@@ -15012,7 +15038,7 @@
       </c>
     </row>
     <row r="185" spans="1:10">
-      <c r="A185" s="1">
+      <c r="A185" s="2">
         <v>45017</v>
       </c>
       <c r="B185">
@@ -15044,7 +15070,7 @@
       </c>
     </row>
     <row r="186" spans="1:10">
-      <c r="A186" s="1">
+      <c r="A186" s="2">
         <v>45047</v>
       </c>
       <c r="B186">
@@ -15076,7 +15102,7 @@
       </c>
     </row>
     <row r="187" spans="1:10">
-      <c r="A187" s="1">
+      <c r="A187" s="2">
         <v>45078</v>
       </c>
       <c r="B187">
@@ -15108,7 +15134,7 @@
       </c>
     </row>
     <row r="188" spans="1:10">
-      <c r="A188" s="1">
+      <c r="A188" s="2">
         <v>45108</v>
       </c>
       <c r="B188">
@@ -15140,7 +15166,7 @@
       </c>
     </row>
     <row r="189" spans="1:10">
-      <c r="A189" s="1">
+      <c r="A189" s="2">
         <v>45139</v>
       </c>
       <c r="B189">
@@ -15172,7 +15198,7 @@
       </c>
     </row>
     <row r="190" spans="1:10">
-      <c r="A190" s="1">
+      <c r="A190" s="2">
         <v>45170</v>
       </c>
       <c r="B190">
@@ -15204,7 +15230,7 @@
       </c>
     </row>
     <row r="191" spans="1:10">
-      <c r="A191" s="1">
+      <c r="A191" s="2">
         <v>45200</v>
       </c>
       <c r="B191">
@@ -15236,7 +15262,7 @@
       </c>
     </row>
     <row r="192" spans="1:10">
-      <c r="A192" s="1">
+      <c r="A192" s="2">
         <v>45231</v>
       </c>
       <c r="B192">
@@ -15268,7 +15294,7 @@
       </c>
     </row>
     <row r="193" spans="1:10">
-      <c r="A193" s="1">
+      <c r="A193" s="2">
         <v>45261</v>
       </c>
       <c r="B193">
@@ -15300,7 +15326,7 @@
       </c>
     </row>
     <row r="194" spans="1:10">
-      <c r="A194" s="1">
+      <c r="A194" s="2">
         <v>45292</v>
       </c>
       <c r="B194">
@@ -15332,7 +15358,7 @@
       </c>
     </row>
     <row r="195" spans="1:10">
-      <c r="A195" s="1">
+      <c r="A195" s="2">
         <v>45323</v>
       </c>
       <c r="B195">
@@ -15364,7 +15390,7 @@
       </c>
     </row>
     <row r="196" spans="1:10">
-      <c r="A196" s="1">
+      <c r="A196" s="2">
         <v>45352</v>
       </c>
       <c r="B196">
@@ -15396,7 +15422,7 @@
       </c>
     </row>
     <row r="197" spans="1:10">
-      <c r="A197" s="1">
+      <c r="A197" s="2">
         <v>45383</v>
       </c>
       <c r="B197">
@@ -15428,7 +15454,7 @@
       </c>
     </row>
     <row r="198" spans="1:10">
-      <c r="A198" s="1">
+      <c r="A198" s="2">
         <v>45413</v>
       </c>
       <c r="B198">
@@ -15460,7 +15486,7 @@
       </c>
     </row>
     <row r="199" spans="1:10">
-      <c r="A199" s="1">
+      <c r="A199" s="2">
         <v>45444</v>
       </c>
       <c r="B199">
@@ -15492,7 +15518,7 @@
       </c>
     </row>
     <row r="200" spans="1:10">
-      <c r="A200" s="1">
+      <c r="A200" s="2">
         <v>45474</v>
       </c>
       <c r="B200">
@@ -15524,7 +15550,7 @@
       </c>
     </row>
     <row r="201" spans="1:10">
-      <c r="A201" s="1">
+      <c r="A201" s="2">
         <v>45505</v>
       </c>
       <c r="B201">
@@ -15556,7 +15582,7 @@
       </c>
     </row>
     <row r="202" spans="1:10">
-      <c r="A202" s="1">
+      <c r="A202" s="2">
         <v>45536</v>
       </c>
       <c r="B202">
@@ -15588,7 +15614,7 @@
       </c>
     </row>
     <row r="203" spans="1:10">
-      <c r="A203" s="1">
+      <c r="A203" s="2">
         <v>45566</v>
       </c>
       <c r="B203">
@@ -15620,7 +15646,7 @@
       </c>
     </row>
     <row r="204" spans="1:10">
-      <c r="A204" s="1">
+      <c r="A204" s="2">
         <v>45597</v>
       </c>
       <c r="B204">
@@ -15652,7 +15678,7 @@
       </c>
     </row>
     <row r="205" spans="1:10">
-      <c r="A205" s="1">
+      <c r="A205" s="2">
         <v>45627</v>
       </c>
       <c r="B205">
@@ -15684,7 +15710,7 @@
       </c>
     </row>
     <row r="206" spans="1:10">
-      <c r="A206" s="1">
+      <c r="A206" s="2">
         <v>45658</v>
       </c>
       <c r="B206">
@@ -15716,7 +15742,7 @@
       </c>
     </row>
     <row r="207" spans="1:10">
-      <c r="A207" s="1">
+      <c r="A207" s="2">
         <v>45689</v>
       </c>
       <c r="B207">
@@ -15748,7 +15774,7 @@
       </c>
     </row>
     <row r="208" spans="1:10">
-      <c r="A208" s="1">
+      <c r="A208" s="2">
         <v>45717</v>
       </c>
       <c r="B208">
@@ -15780,7 +15806,7 @@
       </c>
     </row>
     <row r="209" spans="1:10">
-      <c r="A209" s="1">
+      <c r="A209" s="2">
         <v>45748</v>
       </c>
       <c r="B209">
@@ -15812,7 +15838,7 @@
       </c>
     </row>
     <row r="210" spans="1:10">
-      <c r="A210" s="1">
+      <c r="A210" s="2">
         <v>45778</v>
       </c>
       <c r="B210">
@@ -15844,7 +15870,7 @@
       </c>
     </row>
     <row r="211" spans="1:10">
-      <c r="A211" s="1">
+      <c r="A211" s="2">
         <v>45809</v>
       </c>
       <c r="B211">
@@ -15876,7 +15902,7 @@
       </c>
     </row>
     <row r="212" spans="1:10">
-      <c r="A212" s="1">
+      <c r="A212" s="2">
         <v>45839</v>
       </c>
       <c r="B212">
@@ -15908,7 +15934,7 @@
       </c>
     </row>
     <row r="213" spans="1:10">
-      <c r="A213" s="1">
+      <c r="A213" s="2">
         <v>45870</v>
       </c>
       <c r="B213">
@@ -15940,7 +15966,7 @@
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="A214" s="1">
+      <c r="A214" s="2">
         <v>45901</v>
       </c>
       <c r="B214">
@@ -15972,7 +15998,7 @@
       </c>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" s="1">
+      <c r="A215" s="2">
         <v>45931</v>
       </c>
       <c r="B215">
@@ -16004,7 +16030,7 @@
       </c>
     </row>
     <row r="216" spans="1:10">
-      <c r="A216" s="1">
+      <c r="A216" s="2">
         <v>45962</v>
       </c>
       <c r="B216">
@@ -16036,7 +16062,7 @@
       </c>
     </row>
     <row r="217" spans="1:10">
-      <c r="A217" s="1">
+      <c r="A217" s="2">
         <v>45992</v>
       </c>
       <c r="B217">
@@ -16068,7 +16094,7 @@
       </c>
     </row>
     <row r="218" spans="1:10">
-      <c r="A218" s="1">
+      <c r="A218" s="2">
         <v>46023</v>
       </c>
       <c r="B218">
@@ -16100,7 +16126,7 @@
       </c>
     </row>
     <row r="219" spans="1:10">
-      <c r="A219" s="1">
+      <c r="A219" s="2">
         <v>46054</v>
       </c>
       <c r="B219">
@@ -16132,7 +16158,7 @@
       </c>
     </row>
     <row r="220" spans="1:10">
-      <c r="A220" s="1">
+      <c r="A220" s="2">
         <v>46082</v>
       </c>
       <c r="B220">
@@ -16164,7 +16190,7 @@
       </c>
     </row>
     <row r="221" spans="1:10">
-      <c r="A221" s="1">
+      <c r="A221" s="2">
         <v>46113</v>
       </c>
       <c r="B221">
@@ -16196,7 +16222,7 @@
       </c>
     </row>
     <row r="222" spans="1:10">
-      <c r="A222" s="1">
+      <c r="A222" s="2">
         <v>46143</v>
       </c>
       <c r="B222">
@@ -16228,7 +16254,7 @@
       </c>
     </row>
     <row r="223" spans="1:10">
-      <c r="A223" s="1">
+      <c r="A223" s="2">
         <v>46174</v>
       </c>
       <c r="B223">
@@ -16260,7 +16286,7 @@
       </c>
     </row>
     <row r="224" spans="1:10">
-      <c r="A224" s="1">
+      <c r="A224" s="2">
         <v>46204</v>
       </c>
       <c r="B224">
@@ -16292,7 +16318,7 @@
       </c>
     </row>
     <row r="225" spans="1:10">
-      <c r="A225" s="1">
+      <c r="A225" s="2">
         <v>46235</v>
       </c>
       <c r="B225">
@@ -16324,7 +16350,7 @@
       </c>
     </row>
     <row r="226" spans="1:10">
-      <c r="A226" s="1">
+      <c r="A226" s="2">
         <v>46266</v>
       </c>
       <c r="B226">
@@ -16366,19 +16392,19 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
